--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,7 +47,7 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
@@ -66,6 +65,27 @@
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>BRINDA SOPORTE TÉCNICO A DISTANCIA</t>
+  </si>
+  <si>
+    <t>INSTALA UNA RED LAN</t>
+  </si>
+  <si>
+    <t>OPERA UNA RED LAN</t>
+  </si>
+  <si>
+    <t>INSTALA Y CONFIGURA SOFTWARE</t>
+  </si>
+  <si>
+    <t>BRINDA SOPORTE TÉCNICO DE MANERA PRESENCIAL</t>
+  </si>
+  <si>
+    <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
+  </si>
+  <si>
     <t>4ASV</t>
   </si>
   <si>
@@ -73,24 +93,6 @@
   </si>
   <si>
     <t>2ASV</t>
-  </si>
-  <si>
-    <t>BRINDA SOPORTE TÉCNICO A DISTANCIA</t>
-  </si>
-  <si>
-    <t>INSTALA UNA RED LAN</t>
-  </si>
-  <si>
-    <t>OPERA UNA RED LAN</t>
-  </si>
-  <si>
-    <t>INSTALA Y CONFIGURA SOFTWARE</t>
-  </si>
-  <si>
-    <t>BRINDA SOPORTE TÉCNICO DE MANERA PRESENCIAL</t>
-  </si>
-  <si>
-    <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
   </si>
 </sst>
 </file>
@@ -454,11 +456,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -504,10 +506,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -539,10 +541,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>19</v>
@@ -554,10 +556,10 @@
         <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>78.95</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>21.05</v>
+        <v>21.1</v>
       </c>
       <c r="I3" s="2">
         <v>6.6</v>
@@ -571,31 +573,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -606,31 +602,31 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>19</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>57.58</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>42.42</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -641,31 +637,25 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -676,36 +666,222 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>33</v>
       </c>
       <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="H7" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
         <v>33</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
         <v>100</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
         <v>8.800000000000001</v>
       </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>132</v>
+      </c>
+      <c r="E13">
+        <v>110</v>
+      </c>
+      <c r="F13">
+        <v>22</v>
+      </c>
+      <c r="G13" s="1">
+        <v>83.3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -716,11 +892,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -766,31 +942,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>14</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -798,420 +977,347 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>21.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>12.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.6</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F7">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="H7" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
         <v>33</v>
       </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="E8">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <v>57.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
         <v>100</v>
       </c>
-      <c r="J7">
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
         <v>33</v>
       </c>
-      <c r="K7" s="1">
+      <c r="E12">
+        <v>33</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
         <v>100</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>14</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>100</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>8.9</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>19</v>
-      </c>
-      <c r="E3">
-        <v>15</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1">
-        <v>78.95</v>
-      </c>
-      <c r="H3" s="1">
-        <v>21.05</v>
-      </c>
-      <c r="I3" s="2">
-        <v>6.6</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8.6</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D13">
+        <v>132</v>
+      </c>
+      <c r="E13">
+        <v>110</v>
+      </c>
+      <c r="F13">
         <v>22</v>
       </c>
-      <c r="D5">
-        <v>33</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>14</v>
-      </c>
-      <c r="G5" s="1">
-        <v>57.58</v>
-      </c>
-      <c r="H5" s="1">
-        <v>42.42</v>
-      </c>
-      <c r="I5" s="2">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" s="1">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="H6" s="1">
-        <v>28.57</v>
-      </c>
-      <c r="I6" s="2">
-        <v>7.4</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>100</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="G13" s="1">
+        <v>83.3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>16.7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="27">
   <si>
     <t>Docente</t>
   </si>
@@ -65,15 +65,15 @@
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>BRINDA SOPORTE TÉCNICO A DISTANCIA</t>
   </si>
   <si>
     <t>INSTALA UNA RED LAN</t>
   </si>
   <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
     <t>OPERA UNA RED LAN</t>
   </si>
   <si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>ENSAMBLA E INSTALA CONTROLADORES Y DISPOSITIVOS PERIFÉRICOS</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>4ASV</t>
@@ -460,7 +463,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -506,10 +509,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -541,10 +544,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>19</v>
@@ -575,6 +578,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
       <c r="D4">
         <v>33</v>
       </c>
@@ -608,7 +614,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>19</v>
@@ -639,6 +645,9 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
       <c r="D6">
         <v>19</v>
       </c>
@@ -672,7 +681,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>33</v>
@@ -703,6 +712,9 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
       <c r="D8">
         <v>33</v>
       </c>
@@ -736,7 +748,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>14</v>
@@ -766,6 +778,9 @@
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
       </c>
       <c r="D10">
         <v>14</v>
@@ -800,7 +815,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>33</v>
@@ -831,6 +846,9 @@
       <c r="A12" t="s">
         <v>15</v>
       </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
       <c r="D12">
         <v>33</v>
       </c>
@@ -857,8 +875,8 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>16</v>
+      <c r="B13" t="s">
+        <v>23</v>
       </c>
       <c r="D13">
         <v>132</v>
@@ -942,10 +960,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -977,10 +995,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3">
         <v>19</v>
@@ -1011,6 +1029,9 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
       <c r="D4">
         <v>33</v>
       </c>
@@ -1044,7 +1065,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <v>19</v>
@@ -1075,6 +1096,9 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
       <c r="D6">
         <v>19</v>
       </c>
@@ -1108,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>33</v>
@@ -1139,6 +1163,9 @@
       <c r="A8" t="s">
         <v>13</v>
       </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
       <c r="D8">
         <v>33</v>
       </c>
@@ -1172,7 +1199,7 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>14</v>
@@ -1202,6 +1229,9 @@
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
       </c>
       <c r="D10">
         <v>14</v>
@@ -1236,7 +1266,7 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>33</v>
@@ -1267,6 +1297,9 @@
       <c r="A12" t="s">
         <v>15</v>
       </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
       <c r="D12">
         <v>33</v>
       </c>
@@ -1293,8 +1326,8 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>16</v>
+      <c r="B13" t="s">
+        <v>23</v>
       </c>
       <c r="D13">
         <v>132</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="27">
   <si>
     <t>Docente</t>
   </si>
@@ -969,6 +970,457 @@
         <v>14</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>14</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>19</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>33</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>19</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>33</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>33</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>33</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>14</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>14</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>14</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>14</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>33</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>33</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>33</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>33</v>
+      </c>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
+        <v>132</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>132</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>132</v>
+      </c>
+      <c r="K13" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
         <v>14</v>
       </c>
       <c r="F2">

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
@@ -970,25 +970,25 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1005,25 +1005,25 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1037,25 +1037,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1072,25 +1072,25 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1104,25 +1104,25 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1139,25 +1139,25 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>15.2</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1171,25 +1171,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>15.2</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1206,25 +1206,25 @@
         <v>14</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1238,25 +1238,25 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1273,25 +1273,25 @@
         <v>33</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1305,25 +1305,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1334,25 +1334,25 @@
         <v>132</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="F13">
-        <v>132</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>7.6</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1456,19 +1456,19 @@
         <v>19</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H3" s="1">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="I3" s="2">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1488,16 +1488,16 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
       <c r="I4" s="2">
         <v>7.8</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1590,19 +1590,19 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>57.6</v>
+        <v>84.8</v>
       </c>
       <c r="H7" s="1">
-        <v>42.4</v>
+        <v>15.2</v>
       </c>
       <c r="I7" s="2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1622,19 +1622,19 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>57.6</v>
+        <v>84.8</v>
       </c>
       <c r="H8" s="1">
-        <v>42.4</v>
+        <v>15.2</v>
       </c>
       <c r="I8" s="2">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1657,19 +1657,19 @@
         <v>14</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>71.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>28.6</v>
+        <v>7.1</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1689,19 +1689,19 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>71.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>28.6</v>
+        <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1724,19 +1724,19 @@
         <v>33</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1756,19 +1756,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1785,19 +1785,19 @@
         <v>132</v>
       </c>
       <c r="E13">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1">
-        <v>83.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>16.7</v>
+        <v>7.6</v>
       </c>
       <c r="I13" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
@@ -914,8 +914,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1365,8 +1364,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1421,19 +1419,19 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1468,7 +1466,7 @@
         <v>15.8</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1488,19 +1486,19 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>9.1</v>
+        <v>12.1</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1535,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1567,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1669,7 +1667,7 @@
         <v>7.1</v>
       </c>
       <c r="I9" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1701,7 +1699,7 @@
         <v>7.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1785,19 +1783,19 @@
         <v>132</v>
       </c>
       <c r="E13">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>92.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H13" s="1">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I13" s="2">
         <v>7.6</v>
-      </c>
-      <c r="I13" s="2">
-        <v>7.8</v>
       </c>
       <c r="J13">
         <v>0</v>

--- a/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
+++ b/academias/Soporte y Mantenimiento a Equipo de Cómputo - Estadisticos 20222.xlsx
@@ -1588,19 +1588,19 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>84.8</v>
+        <v>97</v>
       </c>
       <c r="H7" s="1">
-        <v>15.2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1620,19 +1620,19 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>84.8</v>
+        <v>97</v>
       </c>
       <c r="H8" s="1">
-        <v>15.2</v>
+        <v>3</v>
       </c>
       <c r="I8" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1722,19 +1722,19 @@
         <v>33</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>97</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="I11" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1754,19 +1754,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>97</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="I12" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1783,16 +1783,16 @@
         <v>132</v>
       </c>
       <c r="E13">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>91.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>8.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="I13" s="2">
         <v>7.6</v>
